--- a/preview/pr-13/CodeSystem-mhi-gewichtsmethode.xlsx
+++ b/preview/pr-13/CodeSystem-mhi-gewichtsmethode.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T07:34:58+00:00</t>
+    <t>2026-09-30T07:33:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-13/CodeSystem-mhi-gewichtsmethode.xlsx
+++ b/preview/pr-13/CodeSystem-mhi-gewichtsmethode.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T07:33:31+00:00</t>
+    <t>2026-09-30T08:17:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/preview/pr-13/CodeSystem-mhi-gewichtsmethode.xlsx
+++ b/preview/pr-13/CodeSystem-mhi-gewichtsmethode.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T08:17:00+00:00</t>
+    <t>2026-09-30T08:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
